--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/161.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/161.xlsx
@@ -426,13 +426,13 @@
         <v>-10.97637206450313</v>
       </c>
       <c r="E2">
-        <v>-15.32493323486307</v>
+        <v>-16.00892300592961</v>
       </c>
       <c r="F2">
-        <v>1.037206133104378</v>
+        <v>0.7294394784726669</v>
       </c>
       <c r="G2">
-        <v>-8.464417227659062</v>
+        <v>-10.05252564939392</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.16889543518349</v>
       </c>
       <c r="E3">
-        <v>-14.32529524003987</v>
+        <v>-16.91969875530029</v>
       </c>
       <c r="F3">
-        <v>1.023970478742448</v>
+        <v>0.3993110458023827</v>
       </c>
       <c r="G3">
-        <v>-8.000914367796781</v>
+        <v>-9.313711201394771</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.410067972329655</v>
       </c>
       <c r="E4">
-        <v>-14.85648976961361</v>
+        <v>-16.69439811647067</v>
       </c>
       <c r="F4">
-        <v>0.8655534966310705</v>
+        <v>0.3835969161712761</v>
       </c>
       <c r="G4">
-        <v>-7.299194582565165</v>
+        <v>-8.977177694600158</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.809106483947646</v>
       </c>
       <c r="E5">
-        <v>-15.86719988338556</v>
+        <v>-17.84128397212728</v>
       </c>
       <c r="F5">
-        <v>0.737272520633539</v>
+        <v>0.9019751545973591</v>
       </c>
       <c r="G5">
-        <v>-6.472028295213944</v>
+        <v>-8.947117941103576</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.368736600042984</v>
       </c>
       <c r="E6">
-        <v>-16.29211565647329</v>
+        <v>-17.85228816396592</v>
       </c>
       <c r="F6">
-        <v>0.9114533344201911</v>
+        <v>0.7108078388489004</v>
       </c>
       <c r="G6">
-        <v>-6.990595459030922</v>
+        <v>-9.461811766639606</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.108481938808577</v>
       </c>
       <c r="E7">
-        <v>-15.39637444080807</v>
+        <v>-18.08877413359448</v>
       </c>
       <c r="F7">
-        <v>0.9689320917656432</v>
+        <v>0.968879076251864</v>
       </c>
       <c r="G7">
-        <v>-5.927248231817017</v>
+        <v>-8.510999913942147</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.026709700096752</v>
       </c>
       <c r="E8">
-        <v>-16.42580979460174</v>
+        <v>-19.08672300761281</v>
       </c>
       <c r="F8">
-        <v>1.306698900257142</v>
+        <v>1.040673679052497</v>
       </c>
       <c r="G8">
-        <v>-5.887637554439637</v>
+        <v>-8.025389230968614</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.11289587742499</v>
       </c>
       <c r="E9">
-        <v>-18.0161691098295</v>
+        <v>-19.17754155383664</v>
       </c>
       <c r="F9">
-        <v>1.229344295448918</v>
+        <v>1.034941376625125</v>
       </c>
       <c r="G9">
-        <v>-5.248589706811963</v>
+        <v>-7.974377034753984</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.341315702571597</v>
       </c>
       <c r="E10">
-        <v>-17.32529152979728</v>
+        <v>-20.83087382861506</v>
       </c>
       <c r="F10">
-        <v>1.49169653558955</v>
+        <v>0.8602270942310697</v>
       </c>
       <c r="G10">
-        <v>-5.203642430025278</v>
+        <v>-7.652350338512457</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.685685183739976</v>
       </c>
       <c r="E11">
-        <v>-19.62405814794095</v>
+        <v>-21.30413559020868</v>
       </c>
       <c r="F11">
-        <v>1.45224470966382</v>
+        <v>1.261776536003324</v>
       </c>
       <c r="G11">
-        <v>-5.868509222313729</v>
+        <v>-7.150445150394631</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.101710652382648</v>
       </c>
       <c r="E12">
-        <v>-19.8936608479876</v>
+        <v>-22.10430336194201</v>
       </c>
       <c r="F12">
-        <v>1.837791749948794</v>
+        <v>0.934962401311641</v>
       </c>
       <c r="G12">
-        <v>-4.42724997960986</v>
+        <v>-7.160277470646267</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.549238586595683</v>
       </c>
       <c r="E13">
-        <v>-20.60330895278161</v>
+        <v>-22.16409733273928</v>
       </c>
       <c r="F13">
-        <v>1.69542521463406</v>
+        <v>1.180609784407418</v>
       </c>
       <c r="G13">
-        <v>-4.429633572398135</v>
+        <v>-6.546025609107734</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.99305013199263</v>
       </c>
       <c r="E14">
-        <v>-21.51470963156535</v>
+        <v>-22.82489225993854</v>
       </c>
       <c r="F14">
-        <v>1.575426255929718</v>
+        <v>1.741223991600039</v>
       </c>
       <c r="G14">
-        <v>-4.57737328817919</v>
+        <v>-6.34140741041646</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.39570896837434</v>
       </c>
       <c r="E15">
-        <v>-22.55094675331853</v>
+        <v>-23.8141192930181</v>
       </c>
       <c r="F15">
-        <v>1.663074154085128</v>
+        <v>1.671410843626902</v>
       </c>
       <c r="G15">
-        <v>-4.68802827282933</v>
+        <v>-6.008965737908387</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.7331595597251</v>
       </c>
       <c r="E16">
-        <v>-22.86650893606904</v>
+        <v>-24.41080008521676</v>
       </c>
       <c r="F16">
-        <v>2.187207060858459</v>
+        <v>1.907598270982709</v>
       </c>
       <c r="G16">
-        <v>-4.416043782959427</v>
+        <v>-5.528294388879447</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.98095470059554</v>
       </c>
       <c r="E17">
-        <v>-23.52921940777354</v>
+        <v>-23.88603146025991</v>
       </c>
       <c r="F17">
-        <v>1.416050024365899</v>
+        <v>2.295984954724479</v>
       </c>
       <c r="G17">
-        <v>-3.243544558770211</v>
+        <v>-5.182789303673409</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.12820322080694</v>
       </c>
       <c r="E18">
-        <v>-23.54281841521857</v>
+        <v>-26.26598908888709</v>
       </c>
       <c r="F18">
-        <v>2.580328692674632</v>
+        <v>1.71515858290355</v>
       </c>
       <c r="G18">
-        <v>-2.495026901795457</v>
+        <v>-4.413557563259435</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.17417634125765</v>
       </c>
       <c r="E19">
-        <v>-24.51058048150177</v>
+        <v>-26.95743725664427</v>
       </c>
       <c r="F19">
-        <v>2.542122731322713</v>
+        <v>2.182102660922409</v>
       </c>
       <c r="G19">
-        <v>-3.101383112222828</v>
+        <v>-4.682138812314967</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.11974740853573</v>
       </c>
       <c r="E20">
-        <v>-26.10878311371082</v>
+        <v>-27.33422893645249</v>
       </c>
       <c r="F20">
-        <v>2.762249771473043</v>
+        <v>2.63102146425635</v>
       </c>
       <c r="G20">
-        <v>-2.368183349458281</v>
+        <v>-3.657018454443026</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.97549752901345</v>
       </c>
       <c r="E21">
-        <v>-25.43035430872569</v>
+        <v>-27.70106250191783</v>
       </c>
       <c r="F21">
-        <v>3.017575799303128</v>
+        <v>2.680864330882797</v>
       </c>
       <c r="G21">
-        <v>-2.343715107377528</v>
+        <v>-4.385699322546468</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.75899815741467</v>
       </c>
       <c r="E22">
-        <v>-25.69445038437902</v>
+        <v>-28.39122911153084</v>
       </c>
       <c r="F22">
-        <v>3.000103874043281</v>
+        <v>3.067233111631348</v>
       </c>
       <c r="G22">
-        <v>-1.041826521331437</v>
+        <v>-4.015921317446494</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.48524412675329</v>
       </c>
       <c r="E23">
-        <v>-27.45923746143422</v>
+        <v>-28.90678682035609</v>
       </c>
       <c r="F23">
-        <v>3.230002336077034</v>
+        <v>2.818903474885306</v>
       </c>
       <c r="G23">
-        <v>-2.004198799052032</v>
+        <v>-3.370672818023764</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.17635406279241</v>
       </c>
       <c r="E24">
-        <v>-28.70188695693103</v>
+        <v>-29.13057947734115</v>
       </c>
       <c r="F24">
-        <v>3.190285432582409</v>
+        <v>3.137304710234158</v>
       </c>
       <c r="G24">
-        <v>-1.751044692209504</v>
+        <v>-3.1875433704279</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.848581251982775</v>
       </c>
       <c r="E25">
-        <v>-27.8093790717073</v>
+        <v>-29.81953698439412</v>
       </c>
       <c r="F25">
-        <v>3.102985448736174</v>
+        <v>3.401593673362535</v>
       </c>
       <c r="G25">
-        <v>-0.5759665530451957</v>
+        <v>-3.703432302903608</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.518674953577422</v>
       </c>
       <c r="E26">
-        <v>-28.61359982767749</v>
+        <v>-30.04105861166433</v>
       </c>
       <c r="F26">
-        <v>2.921574644257888</v>
+        <v>3.02033094928484</v>
       </c>
       <c r="G26">
-        <v>0.616531676746757</v>
+        <v>-2.966041389486343</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.207394112669771</v>
       </c>
       <c r="E27">
-        <v>-28.09292494322357</v>
+        <v>-30.67359812529273</v>
       </c>
       <c r="F27">
-        <v>3.092460212516204</v>
+        <v>3.169591158125671</v>
       </c>
       <c r="G27">
-        <v>-0.7901025701618739</v>
+        <v>-3.412630672188487</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.925590616950855</v>
       </c>
       <c r="E28">
-        <v>-30.04337492611925</v>
+        <v>-29.86245559680181</v>
       </c>
       <c r="F28">
-        <v>3.42308649399557</v>
+        <v>2.40762734306938</v>
       </c>
       <c r="G28">
-        <v>-1.219990150618395</v>
+        <v>-2.960022817695948</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.683871961632315</v>
       </c>
       <c r="E29">
-        <v>-29.55367027540379</v>
+        <v>-29.19533665565084</v>
       </c>
       <c r="F29">
-        <v>2.761446255092327</v>
+        <v>2.826444931720393</v>
       </c>
       <c r="G29">
-        <v>-0.2083139181814341</v>
+        <v>-3.235665460386746</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.494708521158232</v>
       </c>
       <c r="E30">
-        <v>-28.57637124286043</v>
+        <v>-29.94851018836957</v>
       </c>
       <c r="F30">
-        <v>2.931862967400658</v>
+        <v>2.468331763081333</v>
       </c>
       <c r="G30">
-        <v>-0.3072230872582393</v>
+        <v>-2.752392022563938</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.359504470253638</v>
       </c>
       <c r="E31">
-        <v>-27.57679664667335</v>
+        <v>-29.34897419330907</v>
       </c>
       <c r="F31">
-        <v>2.888832594294835</v>
+        <v>2.584606381942689</v>
       </c>
       <c r="G31">
-        <v>-1.012544746036584</v>
+        <v>-2.688160818010998</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.283161534426036</v>
       </c>
       <c r="E32">
-        <v>-27.88654879727201</v>
+        <v>-29.73406656597335</v>
       </c>
       <c r="F32">
-        <v>2.926684014398356</v>
+        <v>2.501529415115926</v>
       </c>
       <c r="G32">
-        <v>-1.55047198016722</v>
+        <v>-3.302492132642474</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.2602863083809</v>
       </c>
       <c r="E33">
-        <v>-27.92241883988677</v>
+        <v>-29.33220072558466</v>
       </c>
       <c r="F33">
-        <v>2.800139296477092</v>
+        <v>2.568005899190586</v>
       </c>
       <c r="G33">
-        <v>-0.4413068026898009</v>
+        <v>-3.581382420507297</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.284043609130077</v>
       </c>
       <c r="E34">
-        <v>-28.88360103343682</v>
+        <v>-28.42969396975199</v>
       </c>
       <c r="F34">
-        <v>2.634785565734671</v>
+        <v>2.517876417442772</v>
       </c>
       <c r="G34">
-        <v>-1.000222895539416</v>
+        <v>-3.057568042010574</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.350258802324138</v>
       </c>
       <c r="E35">
-        <v>-27.83152783807881</v>
+        <v>-28.87925822686347</v>
       </c>
       <c r="F35">
-        <v>3.229016578867702</v>
+        <v>2.926152202525758</v>
       </c>
       <c r="G35">
-        <v>-2.469479421868901</v>
+        <v>-3.068661680112672</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.444222479021263</v>
       </c>
       <c r="E36">
-        <v>-26.87472467889418</v>
+        <v>-28.0223939605541</v>
       </c>
       <c r="F36">
-        <v>3.016480697596628</v>
+        <v>2.805185710694946</v>
       </c>
       <c r="G36">
-        <v>-1.735412296173065</v>
+        <v>-3.432997148346084</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.553671914075956</v>
       </c>
       <c r="E37">
-        <v>-26.65804625457516</v>
+        <v>-27.72986359660661</v>
       </c>
       <c r="F37">
-        <v>3.301092826585287</v>
+        <v>2.580782638011366</v>
       </c>
       <c r="G37">
-        <v>-2.049957159495838</v>
+        <v>-2.777151592652147</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.667207949240201</v>
       </c>
       <c r="E38">
-        <v>-25.88330133592089</v>
+        <v>-27.31293605166842</v>
       </c>
       <c r="F38">
-        <v>3.129705267680875</v>
+        <v>3.00593558055899</v>
       </c>
       <c r="G38">
-        <v>-2.413630518621396</v>
+        <v>-3.332085099218019</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.769304311310504</v>
       </c>
       <c r="E39">
-        <v>-26.27314407781921</v>
+        <v>-26.49437814698994</v>
       </c>
       <c r="F39">
-        <v>2.888840877968863</v>
+        <v>2.893164955811476</v>
       </c>
       <c r="G39">
-        <v>-2.140775355274665</v>
+        <v>-2.854664705908643</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.85158540397107</v>
       </c>
       <c r="E40">
-        <v>-24.56388062057205</v>
+        <v>-26.51155917737504</v>
       </c>
       <c r="F40">
-        <v>2.940292434091546</v>
+        <v>2.879723866333652</v>
       </c>
       <c r="G40">
-        <v>-1.067628913264517</v>
+        <v>-3.91918386624345</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.901787484126922</v>
       </c>
       <c r="E41">
-        <v>-23.59309353365173</v>
+        <v>-25.4422868377359</v>
       </c>
       <c r="F41">
-        <v>2.604570036350156</v>
+        <v>2.988466968768754</v>
       </c>
       <c r="G41">
-        <v>-1.829968097865729</v>
+        <v>-4.180130997285423</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.91322646399523</v>
       </c>
       <c r="E42">
-        <v>-24.00051581164782</v>
+        <v>-25.34605676507291</v>
       </c>
       <c r="F42">
-        <v>2.560134752129186</v>
+        <v>2.958309425102435</v>
       </c>
       <c r="G42">
-        <v>-2.465559735950404</v>
+        <v>-4.104766428083915</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.886125082691068</v>
       </c>
       <c r="E43">
-        <v>-21.52609874369464</v>
+        <v>-24.41460853185722</v>
       </c>
       <c r="F43">
-        <v>2.973435413877554</v>
+        <v>3.290385349536701</v>
       </c>
       <c r="G43">
-        <v>-2.778816797058401</v>
+        <v>-2.908100221458019</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.816929031526211</v>
       </c>
       <c r="E44">
-        <v>-23.16188771016735</v>
+        <v>-23.86823908588377</v>
       </c>
       <c r="F44">
-        <v>3.654994575348514</v>
+        <v>2.886988648456203</v>
       </c>
       <c r="G44">
-        <v>-1.688117842599037</v>
+        <v>-3.945280896729525</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.708344252089795</v>
       </c>
       <c r="E45">
-        <v>-22.16080966060971</v>
+        <v>-23.41427315203684</v>
       </c>
       <c r="F45">
-        <v>3.404176522924463</v>
+        <v>3.231751848031746</v>
       </c>
       <c r="G45">
-        <v>-0.9570169657063879</v>
+        <v>-3.78259406783866</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.566617331163473</v>
       </c>
       <c r="E46">
-        <v>-21.76129409823101</v>
+        <v>-23.14530896682527</v>
       </c>
       <c r="F46">
-        <v>3.274760683585097</v>
+        <v>3.040579562078871</v>
       </c>
       <c r="G46">
-        <v>-2.739898023698728</v>
+        <v>-3.342887409312661</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.396700841538003</v>
       </c>
       <c r="E47">
-        <v>-20.61222098962871</v>
+        <v>-22.75157626575436</v>
       </c>
       <c r="F47">
-        <v>3.237064996553302</v>
+        <v>3.101824077637449</v>
       </c>
       <c r="G47">
-        <v>-2.201467586646123</v>
+        <v>-4.128383859961075</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.210463820021598</v>
       </c>
       <c r="E48">
-        <v>-20.11926942304974</v>
+        <v>-22.87285785662779</v>
       </c>
       <c r="F48">
-        <v>3.585202964927851</v>
+        <v>3.19532190639143</v>
       </c>
       <c r="G48">
-        <v>-2.241260344028163</v>
+        <v>-4.006893459760901</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.015141791426435</v>
       </c>
       <c r="E49">
-        <v>-20.66932957533944</v>
+        <v>-21.18619601315291</v>
       </c>
       <c r="F49">
-        <v>3.139201671586569</v>
+        <v>3.008549908082225</v>
       </c>
       <c r="G49">
-        <v>-0.7161284300868593</v>
+        <v>-4.076683070274277</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.820073517048838</v>
       </c>
       <c r="E50">
-        <v>-18.32673638574954</v>
+        <v>-21.0809814480587</v>
       </c>
       <c r="F50">
-        <v>3.551718697771889</v>
+        <v>3.289445980901926</v>
       </c>
       <c r="G50">
-        <v>-2.983504517205999</v>
+        <v>-3.722659951395695</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.639229917698698</v>
       </c>
       <c r="E51">
-        <v>-19.25977864181593</v>
+        <v>-20.37620598129694</v>
       </c>
       <c r="F51">
-        <v>3.024731236928511</v>
+        <v>3.006828560619208</v>
       </c>
       <c r="G51">
-        <v>-2.881122585858498</v>
+        <v>-3.917084980371552</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.47851132512958</v>
       </c>
       <c r="E52">
-        <v>-17.97091154059684</v>
+        <v>-20.32150201528428</v>
       </c>
       <c r="F52">
-        <v>3.295166686185659</v>
+        <v>3.192651249884804</v>
       </c>
       <c r="G52">
-        <v>-1.44072408499484</v>
+        <v>-4.313264586147214</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.346786367276346</v>
       </c>
       <c r="E53">
-        <v>-16.61038586668037</v>
+        <v>-19.12415537376021</v>
       </c>
       <c r="F53">
-        <v>3.978266611025827</v>
+        <v>3.204536665380171</v>
       </c>
       <c r="G53">
-        <v>-2.75624218702611</v>
+        <v>-4.304097685548972</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.251346687305944</v>
       </c>
       <c r="E54">
-        <v>-18.32541859981331</v>
+        <v>-19.40971188773589</v>
       </c>
       <c r="F54">
-        <v>3.342251089360784</v>
+        <v>3.061035266723602</v>
       </c>
       <c r="G54">
-        <v>-2.75887738127537</v>
+        <v>-4.763558369307802</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.195428500026111</v>
       </c>
       <c r="E55">
-        <v>-17.28593909067063</v>
+        <v>-18.54012260946497</v>
       </c>
       <c r="F55">
-        <v>3.827399369423564</v>
+        <v>3.159728615827941</v>
       </c>
       <c r="G55">
-        <v>-2.337090705753446</v>
+        <v>-4.46440754274264</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.185072441727385</v>
       </c>
       <c r="E56">
-        <v>-16.4724847761988</v>
+        <v>-18.42355968850754</v>
       </c>
       <c r="F56">
-        <v>3.058573358802481</v>
+        <v>3.215452891014263</v>
       </c>
       <c r="G56">
-        <v>-2.905359089751502</v>
+        <v>-5.464490244701072</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.216919217357263</v>
       </c>
       <c r="E57">
-        <v>-16.88004743688913</v>
+        <v>-18.70503604740231</v>
       </c>
       <c r="F57">
-        <v>3.323196982361589</v>
+        <v>3.415942653513828</v>
       </c>
       <c r="G57">
-        <v>-2.571133033197762</v>
+        <v>-4.305355692853895</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.28930126082762</v>
       </c>
       <c r="E58">
-        <v>-16.81796658671798</v>
+        <v>-17.96135646044065</v>
       </c>
       <c r="F58">
-        <v>3.452339460458032</v>
+        <v>2.917881782376208</v>
       </c>
       <c r="G58">
-        <v>-2.290849005660906</v>
+        <v>-4.404420457571046</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.402109628501737</v>
       </c>
       <c r="E59">
-        <v>-16.58653892255598</v>
+        <v>-17.25313482495907</v>
       </c>
       <c r="F59">
-        <v>3.345122210778887</v>
+        <v>3.152579805141781</v>
       </c>
       <c r="G59">
-        <v>-2.448692506427817</v>
+        <v>-4.805397043833112</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.54711426292196</v>
       </c>
       <c r="E60">
-        <v>-15.14145305349429</v>
+        <v>-18.17327998705161</v>
       </c>
       <c r="F60">
-        <v>3.420969186914015</v>
+        <v>3.142428990987876</v>
       </c>
       <c r="G60">
-        <v>-3.22315490879384</v>
+        <v>-5.177667889724156</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.72030785305126</v>
       </c>
       <c r="E61">
-        <v>-14.62489455191334</v>
+        <v>-16.89346983384786</v>
       </c>
       <c r="F61">
-        <v>3.19030365666527</v>
+        <v>3.721838854550018</v>
       </c>
       <c r="G61">
-        <v>-2.700906418337193</v>
+        <v>-5.594554957847959</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.912510466225467</v>
       </c>
       <c r="E62">
-        <v>-15.73260457892958</v>
+        <v>-16.70824618998613</v>
       </c>
       <c r="F62">
-        <v>3.102332695222768</v>
+        <v>3.280532747647804</v>
       </c>
       <c r="G62">
-        <v>-3.293023972400158</v>
+        <v>-5.644888492227039</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.115278279981004</v>
       </c>
       <c r="E63">
-        <v>-16.59436865411524</v>
+        <v>-17.20069056747624</v>
       </c>
       <c r="F63">
-        <v>3.527517115731698</v>
+        <v>2.942093304825232</v>
       </c>
       <c r="G63">
-        <v>-3.695066554325869</v>
+        <v>-5.262613177716315</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.323318114367625</v>
       </c>
       <c r="E64">
-        <v>-14.32190341300813</v>
+        <v>-16.46323763227513</v>
       </c>
       <c r="F64">
-        <v>3.732221611576707</v>
+        <v>3.059499473558811</v>
       </c>
       <c r="G64">
-        <v>-3.503730264338152</v>
+        <v>-5.249711981749776</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.524455265661411</v>
       </c>
       <c r="E65">
-        <v>-14.31931312587574</v>
+        <v>-16.87154296270272</v>
       </c>
       <c r="F65">
-        <v>3.391295409810931</v>
+        <v>3.146300780228561</v>
       </c>
       <c r="G65">
-        <v>-3.261709522144193</v>
+        <v>-5.643428541644219</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.711459404339113</v>
       </c>
       <c r="E66">
-        <v>-13.83802690834053</v>
+        <v>-16.84081726656068</v>
       </c>
       <c r="F66">
-        <v>3.360847937553633</v>
+        <v>3.116532569241557</v>
       </c>
       <c r="G66">
-        <v>-4.376840302683378</v>
+        <v>-5.972900654803567</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.878886795163496</v>
       </c>
       <c r="E67">
-        <v>-13.49397156713377</v>
+        <v>-15.59685904207566</v>
       </c>
       <c r="F67">
-        <v>3.080314689656357</v>
+        <v>2.948983664881718</v>
       </c>
       <c r="G67">
-        <v>-3.22665415542885</v>
+        <v>-5.987390912628957</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.016118515208952</v>
       </c>
       <c r="E68">
-        <v>-13.47390137033178</v>
+        <v>-16.19776037204947</v>
       </c>
       <c r="F68">
-        <v>3.795823660763653</v>
+        <v>3.089715002943326</v>
       </c>
       <c r="G68">
-        <v>-3.881473442005612</v>
+        <v>-5.445150037660651</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.117623985729786</v>
       </c>
       <c r="E69">
-        <v>-12.51195839314843</v>
+        <v>-16.14770714884268</v>
       </c>
       <c r="F69">
-        <v>3.527513802262087</v>
+        <v>3.010463436782692</v>
       </c>
       <c r="G69">
-        <v>-4.524954110110371</v>
+        <v>-6.44088599332602</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.175225780130171</v>
       </c>
       <c r="E70">
-        <v>-14.42586811927622</v>
+        <v>-15.40473400382623</v>
       </c>
       <c r="F70">
-        <v>3.233680287345464</v>
+        <v>2.998074373906423</v>
       </c>
       <c r="G70">
-        <v>-3.498966389307141</v>
+        <v>-5.493589939991266</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.181712410371121</v>
       </c>
       <c r="E71">
-        <v>-13.48255981263444</v>
+        <v>-15.21700611383826</v>
       </c>
       <c r="F71">
-        <v>3.088528780822517</v>
+        <v>2.700534743229674</v>
       </c>
       <c r="G71">
-        <v>-4.64433238225649</v>
+        <v>-5.963127924371638</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.134238605760121</v>
       </c>
       <c r="E72">
-        <v>-14.36996863612554</v>
+        <v>-15.53909382763381</v>
       </c>
       <c r="F72">
-        <v>3.070082695496978</v>
+        <v>2.665416935555391</v>
       </c>
       <c r="G72">
-        <v>-3.207045794199747</v>
+        <v>-5.899423096559443</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.026928917994319</v>
       </c>
       <c r="E73">
-        <v>-13.8856483410052</v>
+        <v>-16.3485042148168</v>
       </c>
       <c r="F73">
-        <v>3.159130534563119</v>
+        <v>2.829203395171715</v>
       </c>
       <c r="G73">
-        <v>-3.59049635237691</v>
+        <v>-6.111394016893438</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.856400522990743</v>
       </c>
       <c r="E74">
-        <v>-14.9184121231945</v>
+        <v>-15.71940860567123</v>
       </c>
       <c r="F74">
-        <v>3.066229130339154</v>
+        <v>2.438720941900862</v>
       </c>
       <c r="G74">
-        <v>-3.106997797457432</v>
+        <v>-5.707994111296625</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.627615508866871</v>
       </c>
       <c r="E75">
-        <v>-14.04928927774637</v>
+        <v>-16.46662493083287</v>
       </c>
       <c r="F75">
-        <v>2.784928814226888</v>
+        <v>2.579864806929064</v>
       </c>
       <c r="G75">
-        <v>-3.017209181341319</v>
+        <v>-4.985487410623924</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.341791767597201</v>
       </c>
       <c r="E76">
-        <v>-13.95523287260706</v>
+        <v>-16.12792224590318</v>
       </c>
       <c r="F76">
-        <v>2.913158431445445</v>
+        <v>2.696051618845723</v>
       </c>
       <c r="G76">
-        <v>-3.630712859587977</v>
+        <v>-4.932949052915691</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.006260853547641</v>
       </c>
       <c r="E77">
-        <v>-15.78959995279012</v>
+        <v>-16.3304990021623</v>
       </c>
       <c r="F77">
-        <v>2.928829485971606</v>
+        <v>2.4833831987902</v>
       </c>
       <c r="G77">
-        <v>-2.92040882977303</v>
+        <v>-5.220503038456786</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.632397731118023</v>
       </c>
       <c r="E78">
-        <v>-15.49902588961394</v>
+        <v>-16.84235694772329</v>
       </c>
       <c r="F78">
-        <v>2.031601557712183</v>
+        <v>2.360092308027133</v>
       </c>
       <c r="G78">
-        <v>-1.938044167540776</v>
+        <v>-4.705259662361237</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.228405049961975</v>
       </c>
       <c r="E79">
-        <v>-13.84680761944141</v>
+        <v>-16.97262755950194</v>
       </c>
       <c r="F79">
-        <v>2.265075253456418</v>
+        <v>2.106267281930919</v>
       </c>
       <c r="G79">
-        <v>-3.036549388381741</v>
+        <v>-4.894987027216868</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.808919222646942</v>
       </c>
       <c r="E80">
-        <v>-16.68107534594011</v>
+        <v>-17.73965595844714</v>
       </c>
       <c r="F80">
-        <v>2.275989822355705</v>
+        <v>2.085185331529672</v>
       </c>
       <c r="G80">
-        <v>-2.333124672197399</v>
+        <v>-4.975224719452184</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.384385284210603</v>
       </c>
       <c r="E81">
-        <v>-16.84773224637039</v>
+        <v>-18.38829646140981</v>
       </c>
       <c r="F81">
-        <v>1.986500266099361</v>
+        <v>1.950095175481129</v>
       </c>
       <c r="G81">
-        <v>-2.467820838553726</v>
+        <v>-4.323027384942525</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.961711040840492</v>
       </c>
       <c r="E82">
-        <v>-16.84042781779602</v>
+        <v>-18.54544356642399</v>
       </c>
       <c r="F82">
-        <v>2.655171687517567</v>
+        <v>2.252754116707179</v>
       </c>
       <c r="G82">
-        <v>-1.685807081812626</v>
+        <v>-4.3066964637973</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.556542986812268</v>
       </c>
       <c r="E83">
-        <v>-17.78712795146955</v>
+        <v>-20.46759964371975</v>
       </c>
       <c r="F83">
-        <v>2.184726928854478</v>
+        <v>1.933150091889462</v>
       </c>
       <c r="G83">
-        <v>-1.299522696653846</v>
+        <v>-3.671257110807431</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.174946192966448</v>
       </c>
       <c r="E84">
-        <v>-19.51791071720116</v>
+        <v>-20.53046391989423</v>
       </c>
       <c r="F84">
-        <v>2.378642767645425</v>
+        <v>1.755044473348346</v>
       </c>
       <c r="G84">
-        <v>-1.836966591135748</v>
+        <v>-4.470042091250479</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.826133587351027</v>
       </c>
       <c r="E85">
-        <v>-18.45719266496251</v>
+        <v>-21.48097702868221</v>
       </c>
       <c r="F85">
-        <v>2.222152568112959</v>
+        <v>1.683440395050357</v>
       </c>
       <c r="G85">
-        <v>-2.322338914830454</v>
+        <v>-3.34044091615914</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.519517922743193</v>
       </c>
       <c r="E86">
-        <v>-20.2312404713634</v>
+        <v>-22.19311579418044</v>
       </c>
       <c r="F86">
-        <v>1.761696263592826</v>
+        <v>1.699969638205818</v>
       </c>
       <c r="G86">
-        <v>-1.556205845041237</v>
+        <v>-3.247272233047431</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.260994817516241</v>
       </c>
       <c r="E87">
-        <v>-23.78923985681996</v>
+        <v>-23.30225681898311</v>
       </c>
       <c r="F87">
-        <v>1.390324246304557</v>
+        <v>1.220891634470752</v>
       </c>
       <c r="G87">
-        <v>-1.347724239705634</v>
+        <v>-3.600010860256776</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.06157208692232</v>
       </c>
       <c r="E88">
-        <v>-22.94616932233796</v>
+        <v>-24.43241449165538</v>
       </c>
       <c r="F88">
-        <v>1.12440174265786</v>
+        <v>1.57308031944499</v>
       </c>
       <c r="G88">
-        <v>-1.46480168270196</v>
+        <v>-2.807121961419169</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.926524259414388</v>
       </c>
       <c r="E89">
-        <v>-24.83704722966274</v>
+        <v>-25.57228121260009</v>
       </c>
       <c r="F89">
-        <v>1.59130771577619</v>
+        <v>1.205633106911185</v>
       </c>
       <c r="G89">
-        <v>-0.9325255498068596</v>
+        <v>-3.826306511139197</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.86269108414996</v>
       </c>
       <c r="E90">
-        <v>-26.39170405581403</v>
+        <v>-27.39455726718267</v>
       </c>
       <c r="F90">
-        <v>1.132040946846477</v>
+        <v>1.151832300834163</v>
       </c>
       <c r="G90">
-        <v>-0.7704677245684566</v>
+        <v>-2.881688689145713</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.880049121575176</v>
       </c>
       <c r="E91">
-        <v>-26.28910694869625</v>
+        <v>-27.77091421348615</v>
       </c>
       <c r="F91">
-        <v>1.103508660024451</v>
+        <v>1.236617361245498</v>
       </c>
       <c r="G91">
-        <v>-0.6667681960963259</v>
+        <v>-3.714072396266825</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.982354766302626</v>
       </c>
       <c r="E92">
-        <v>-29.18387055946342</v>
+        <v>-29.27375624004167</v>
       </c>
       <c r="F92">
-        <v>0.7131123569634886</v>
+        <v>0.5967267368701581</v>
       </c>
       <c r="G92">
-        <v>-0.4906173784972453</v>
+        <v>-3.368944713252265</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.177636599235701</v>
       </c>
       <c r="E93">
-        <v>-30.58816846313803</v>
+        <v>-31.73852765835851</v>
       </c>
       <c r="F93">
-        <v>0.4604097686980687</v>
+        <v>0.4539592717324689</v>
       </c>
       <c r="G93">
-        <v>-0.1742980627654226</v>
+        <v>-3.146774002111775</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.463084285436754</v>
       </c>
       <c r="E94">
-        <v>-32.5028887861132</v>
+        <v>-33.07664417864802</v>
       </c>
       <c r="F94">
-        <v>-0.1001762740028576</v>
+        <v>0.4632088221521282</v>
       </c>
       <c r="G94">
-        <v>-0.7437317587933024</v>
+        <v>-3.034414086508911</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.83790407786967</v>
       </c>
       <c r="E95">
-        <v>-34.06009061465679</v>
+        <v>-35.00476199197488</v>
       </c>
       <c r="F95">
-        <v>-0.1117386262111331</v>
+        <v>0.2023153370078267</v>
       </c>
       <c r="G95">
-        <v>-1.43831731838779</v>
+        <v>-3.816156378515791</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.301472239197222</v>
       </c>
       <c r="E96">
-        <v>-35.9994548931817</v>
+        <v>-36.97053180243852</v>
       </c>
       <c r="F96">
-        <v>-0.2946645146691395</v>
+        <v>-0.3810433539634607</v>
       </c>
       <c r="G96">
-        <v>-0.8182422072456791</v>
+        <v>-3.41824866796863</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.832073519782442</v>
       </c>
       <c r="E97">
-        <v>-38.7657072043222</v>
+        <v>-38.79316107799369</v>
       </c>
       <c r="F97">
-        <v>-0.5592666006757744</v>
+        <v>-0.4741129167701936</v>
       </c>
       <c r="G97">
-        <v>-1.435082915395922</v>
+        <v>-3.421685014238394</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.427838210083489</v>
       </c>
       <c r="E98">
-        <v>-40.5365737577327</v>
+        <v>-40.45013198163728</v>
       </c>
       <c r="F98">
-        <v>-1.215148029394756</v>
+        <v>-0.5685360319131009</v>
       </c>
       <c r="G98">
-        <v>-1.557447299618464</v>
+        <v>-3.419390806179679</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.049657210187749</v>
       </c>
       <c r="E99">
-        <v>-42.21749349616585</v>
+        <v>-42.33182387943751</v>
       </c>
       <c r="F99">
-        <v>-1.415469633311552</v>
+        <v>-0.6210139352478523</v>
       </c>
       <c r="G99">
-        <v>-1.219890834252217</v>
+        <v>-4.003344554942802</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.700254029411192</v>
       </c>
       <c r="E100">
-        <v>-44.52886965018387</v>
+        <v>-45.60903976252247</v>
       </c>
       <c r="F100">
-        <v>-1.318411481460339</v>
+        <v>-1.033658530013204</v>
       </c>
       <c r="G100">
-        <v>-3.020109219233721</v>
+        <v>-3.991052499355488</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.311791717694469</v>
       </c>
       <c r="E101">
-        <v>-45.19622180774624</v>
+        <v>-47.44559409565124</v>
       </c>
       <c r="F101">
-        <v>-1.95015345569434</v>
+        <v>-1.060346042629195</v>
       </c>
       <c r="G101">
-        <v>-1.786556914209266</v>
+        <v>-4.07308119672755</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.927239906073801</v>
       </c>
       <c r="E102">
-        <v>-48.10775888623782</v>
+        <v>-48.80884364668332</v>
       </c>
       <c r="F102">
-        <v>-2.188284232977114</v>
+        <v>-1.581541558592199</v>
       </c>
       <c r="G102">
-        <v>-1.670353455235308</v>
+        <v>-5.013540973523709</v>
       </c>
     </row>
   </sheetData>
